--- a/people_with_ids.xlsx
+++ b/people_with_ids.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,25 +428,81 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>National ID
+(الرقم القومي)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Faculty</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Academic year</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Have you attended an IEEE event before?</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>How did you know about the Event?</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggest to us technological topics you would like us to talk about at the next event. </t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>attended</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>attend_time</t>
         </is>
@@ -454,21 +514,72 @@
           <t>P0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">noouh </t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>46114.0103465625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>noouhfff@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1001111111</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>dima.ahmed4444@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>deema</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Eweis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30707272300403</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1061234987</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>High school</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Computers &amp; Information</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Preparatory</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>noo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>deema Eweis</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -476,21 +587,72 @@
           <t>P0002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nnouh </t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>46116.10074964121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>noouhehab1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1002222222</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>noouhfff@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kenzy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ashraf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>30708150101767</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1157732550</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fayoum University</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Computers &amp; Information</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analysis </t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Kenzy Ashraf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,21 +660,68 @@
           <t>P0003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> dima</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>46117.50828137731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dima.ahmed4444@example.com</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1003333333</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>arwaeldeeb499@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Malk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Amr</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>30611252302909</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1050686556</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fayoum University</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Computers &amp; Information</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Malk Amr</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -520,153 +729,68 @@
           <t>P0004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>فاطمة خالد</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>46117.53712780093</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fatma@example.com</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1004444444</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P0005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>عمر يوسف</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>omar@example.com</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1005555555</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P0006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>نور إبراهيم</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>nour@example.com</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1006666666</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P0007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>كريم عبدالله</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>karim@example.com</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1007777777</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P0008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>هناء سعيد</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hanaa@example.com</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1008888888</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P0009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>طارق رضا</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>tarek@example.com</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1009999999</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P0010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ليلى منصور</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>laila@example.com</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>norhanehab122@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Alaa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ayman</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>30307082101309</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1022410510</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iaet </t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ya </t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Alaa Ayman</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
